--- a/output/pdf_financials_xlsx/EIF.xlsx
+++ b/output/pdf_financials_xlsx/EIF.xlsx
@@ -2100,13 +2100,13 @@
         <v>84.57599999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>414.638</v>
+        <v>94.063</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>460.397</v>
+        <v>10.397</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>513.8630000000001</v>
+        <v>19.596</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>854.487</v>
+        <v>20.897</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>919.63</v>
+        <v>20.244</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>941.229</v>
+        <v>22.51</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1284.338</v>
+        <v>24.739</v>
       </c>
     </row>
     <row r="29">
@@ -2161,13 +2161,13 @@
         <v>144.135</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>501.672</v>
+        <v>181.097</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>555.704</v>
+        <v>105.704</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>602.665</v>
+        <v>108.398</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         <v>284.535</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1082.723</v>
+        <v>183.337</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1109.213</v>
+        <v>190.494</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1512.508</v>
+        <v>252.909</v>
       </c>
     </row>
     <row r="30">
@@ -2222,13 +2222,13 @@
         <v>17.85168001605146</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>56.30273415141646</v>
+        <v>20.32454720737666</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>54.85996347302433</v>
+        <v>10.43526333975024</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>50.08052239004414</v>
+        <v>9.007704887517949</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2244,13 +2244,13 @@
         <v>13.81658397968702</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>43.3363952746041</v>
+        <v>7.338132375926337</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>41.70138294932695</v>
+        <v>7.161711270557672</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>46.14829313240752</v>
+        <v>7.716533511111383</v>
       </c>
     </row>
     <row r="31">
@@ -45046,7 +45046,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -45136,7 +45136,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -47830,7 +47830,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -52954,7 +52954,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -54482,7 +54482,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -54580,7 +54580,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -56178,7 +56178,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -56654,7 +56654,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -56752,7 +56752,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">

--- a/output/pdf_financials_xlsx/EIF.xlsx
+++ b/output/pdf_financials_xlsx/EIF.xlsx
@@ -2100,13 +2100,13 @@
         <v>84.57599999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>94.063</v>
+        <v>414.638</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>10.397</v>
+        <v>460.397</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>19.596</v>
+        <v>513.8630000000001</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>20.897</v>
+        <v>854.487</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>20.244</v>
+        <v>919.63</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>22.51</v>
+        <v>941.229</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>24.739</v>
+        <v>1284.338</v>
       </c>
     </row>
     <row r="29">
@@ -2161,13 +2161,13 @@
         <v>144.135</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>181.097</v>
+        <v>501.672</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>105.704</v>
+        <v>555.704</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>108.398</v>
+        <v>602.665</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         <v>284.535</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>183.337</v>
+        <v>1082.723</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>190.494</v>
+        <v>1109.213</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>252.909</v>
+        <v>1512.508</v>
       </c>
     </row>
     <row r="30">
@@ -2222,13 +2222,13 @@
         <v>17.85168001605146</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>20.32454720737666</v>
+        <v>56.30273415141646</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.43526333975024</v>
+        <v>54.85996347302433</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>9.007704887517949</v>
+        <v>50.08052239004414</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2244,13 +2244,13 @@
         <v>13.81658397968702</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>7.338132375926337</v>
+        <v>43.3363952746041</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>7.161711270557672</v>
+        <v>41.70138294932695</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>7.716533511111383</v>
+        <v>46.14829313240752</v>
       </c>
     </row>
     <row r="31">
@@ -45046,7 +45046,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -45136,7 +45136,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -47830,7 +47830,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -52954,7 +52954,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -54482,7 +54482,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -54580,7 +54580,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -56178,7 +56178,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -56654,7 +56654,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -56752,7 +56752,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">

--- a/output/pdf_financials_xlsx/EIF.xlsx
+++ b/output/pdf_financials_xlsx/EIF.xlsx
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>9.33</v>
+        <v>1.417</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>10.472</v>
+        <v>1.099</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -2100,13 +2100,13 @@
         <v>84.57599999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>414.638</v>
+        <v>11.747</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>460.397</v>
+        <v>10.397</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>513.8630000000001</v>
+        <v>19.596</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>854.487</v>
+        <v>51.552</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>919.63</v>
+        <v>57.335</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>941.229</v>
+        <v>62.569</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1284.338</v>
+        <v>74.018</v>
       </c>
     </row>
     <row r="29">
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>22.923</v>
+        <v>15.01</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>24.403</v>
+        <v>15.03</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2161,13 +2161,13 @@
         <v>144.135</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>501.672</v>
+        <v>98.78100000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>555.704</v>
+        <v>105.704</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>602.665</v>
+        <v>108.398</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         <v>284.535</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1082.723</v>
+        <v>220.428</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1109.213</v>
+        <v>230.553</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1512.508</v>
+        <v>302.188</v>
       </c>
     </row>
     <row r="30">
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10.85107289432949</v>
+        <v>7.105291809269541</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>9.972864066957097</v>
+        <v>6.142365566789541</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2222,13 +2222,13 @@
         <v>17.85168001605146</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>56.30273415141646</v>
+        <v>11.08620848325414</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>54.85996347302433</v>
+        <v>10.43526333975024</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>50.08052239004414</v>
+        <v>9.007704887517949</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2244,13 +2244,13 @@
         <v>13.81658397968702</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>43.3363952746041</v>
+        <v>8.822713600422668</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>41.70138294932695</v>
+        <v>8.667748162991398</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>46.14829313240752</v>
+        <v>9.220090343387252</v>
       </c>
     </row>
     <row r="31">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.417</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.099</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -6612,13 +6612,13 @@
         <v>84.57599999999999</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>94.063</v>
+        <v>11.747</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>10.397</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>19.596</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -6631,16 +6631,16 @@
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>51.552</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>57.335</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>62.569</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>74.018</v>
       </c>
     </row>
     <row r="101">
@@ -7828,19 +7828,19 @@
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>7.714</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>102.158</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>8.712999999999999</v>
       </c>
       <c r="L120" s="1" t="inlineStr">
         <is>
@@ -7853,16 +7853,16 @@
         </is>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>127.114</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>0</v>
+        <v>187.113</v>
       </c>
       <c r="P120" s="3" t="n">
-        <v>0</v>
+        <v>24.245</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>0</v>
+        <v>23.486</v>
       </c>
     </row>
     <row r="121">
@@ -31732,7 +31732,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -31824,7 +31824,11 @@
           <t>Depreciation of right of use assets (Note 10)</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -32866,7 +32870,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -35188,7 +35196,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">
@@ -38070,7 +38078,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -39972,7 +39984,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -45562,7 +45578,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -45736,7 +45752,11 @@
           <t>Depreciation of right of use assets (Note 10)</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -51090,7 +51110,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -57988,7 +58008,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E529" s="5" t="n">

--- a/output/pdf_financials_xlsx/EIF.xlsx
+++ b/output/pdf_financials_xlsx/EIF.xlsx
@@ -4021,10 +4021,8 @@
       <c r="L60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M60" s="3" t="n">
+        <v>2.021</v>
       </c>
       <c r="N60" s="3" t="n">
         <v>626.341</v>
@@ -7565,10 +7563,10 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.649</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
@@ -7576,25 +7574,25 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-2.494</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.188</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.297</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-1.043</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-1.361</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-2.219</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-4.528</v>
       </c>
       <c r="L116" s="1" t="inlineStr">
         <is>
@@ -7607,16 +7605,16 @@
         </is>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-6.945</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-2.569</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-2.157</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-1.857</v>
       </c>
     </row>
     <row r="117">
@@ -32080,7 +32078,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -33296,7 +33298,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E265" s="5" t="n">
         <v>-0.027</v>
       </c>
@@ -38652,7 +38658,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -40364,7 +40374,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -43674,7 +43688,11 @@
           <t>Future income tax</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E376" s="5" t="n">
         <v>0.634</v>
       </c>
